--- a/OHIGGINS/Gastos_OHIGGINS_2026.xlsx
+++ b/OHIGGINS/Gastos_OHIGGINS_2026.xlsx
@@ -160,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -181,6 +181,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -697,6 +698,12 @@
       <c r="I5" t="n">
         <v>829490</v>
       </c>
+      <c r="J5" t="n">
+        <v>907569</v>
+      </c>
+      <c r="K5" t="n">
+        <v>722979</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -816,7 +823,9 @@
       </c>
       <c r="J8" s="5" t="n"/>
       <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
+      <c r="L8" s="5" t="n">
+        <v>18236</v>
+      </c>
       <c r="M8" s="5" t="n"/>
       <c r="N8" s="5" t="n"/>
       <c r="O8" s="5" t="n"/>
@@ -1172,7 +1181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2020,6 +2029,105 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="18" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SERVICIOS</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EXPENSAS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Expensas OHIGGINS 2219 piso 8 · julio (pago 10-ago)</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>907569</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mercado Pago — Consorcio De Copropi</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Kalmus · Gmail Sent · recibo $907.568,08</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SERVICIOS</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EXPENSAS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Expensas OHIGGINS 2219 piso 8 · agosto (pago 11-sep)</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>722979</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mercado Pago — Consorcio De Copropi</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Kalmus · Gmail Sent · MP $722.978,08 · Galicia</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SERVICIOS</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>LUZ</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Edenor — Marta Chagas · cobro BBVA 09/09/2026</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>18236</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Débito BBVA Visa 3200</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>cuenta 9267222037</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/OHIGGINS/Gastos_OHIGGINS_2026.xlsx
+++ b/OHIGGINS/Gastos_OHIGGINS_2026.xlsx
@@ -17,10 +17,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -160,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -181,6 +182,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -697,6 +699,12 @@
       <c r="I5" t="n">
         <v>829490</v>
       </c>
+      <c r="K5" t="n">
+        <v>722979</v>
+      </c>
+      <c r="L5" t="n">
+        <v>722979</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -816,7 +824,9 @@
       </c>
       <c r="J8" s="5" t="n"/>
       <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
+      <c r="L8" s="5" t="n">
+        <v>18236</v>
+      </c>
       <c r="M8" s="5" t="n"/>
       <c r="N8" s="5" t="n"/>
       <c r="O8" s="5" t="n"/>
@@ -1172,7 +1182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2020,6 +2030,171 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="18" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SERVICIOS</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>LUZ</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Edenor Chagas — débito BBVA 09/09/2026</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>18236</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Débito BBVA</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>cuenta 9267222037 · Gmail + Compra aprobada</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SERVICIOS</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EXPENSAS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Expensas — O'Higgins 2219 piso 8 · período agosto 2026</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>722979</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Recibo Kalmus 10/09/2026 · $722.978,08</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SERVICIOS</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EXPENSAS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Expensas — O'Higgins 2219 piso 8 · período septiembre 2026</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>722979</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Liquidación Kalmus sep26 · UF8 ≈ $722.978 · vto ~10/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SERVICIOS</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Metrogas INVALMAR — factura disponible 01/10/2026</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5589</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Factura digital Gmail</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>cliente 10139236800 · $5.588,63 · mes cobro a confirmar</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SERVICIOS</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>TV CABLE-INTERNET</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Personal — saldo a debitar vto 01/10/2026</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>76044</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Débito automático (pendiente confirmar cobro)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>$76.043,51 · Gmail Personal 10/09</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/OHIGGINS/Gastos_OHIGGINS_2026.xlsx
+++ b/OHIGGINS/Gastos_OHIGGINS_2026.xlsx
@@ -161,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -183,6 +183,7 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -740,7 +741,9 @@
         <v>56200</v>
       </c>
       <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
+      <c r="L6" s="5" t="n">
+        <v>76044</v>
+      </c>
       <c r="M6" s="5" t="n"/>
       <c r="N6" s="5" t="n"/>
       <c r="O6" s="5" t="n"/>
@@ -867,7 +870,9 @@
         <v>5208</v>
       </c>
       <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="n"/>
+      <c r="L9" s="5" t="n">
+        <v>5582</v>
+      </c>
       <c r="M9" s="5" t="n"/>
       <c r="N9" s="5" t="n"/>
       <c r="O9" s="5" t="n"/>
@@ -1182,7 +1187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2195,6 +2200,72 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="19" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>TV CABLE-INTERNET</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Personal — Pago directo</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>76044</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Mercado Pago</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Personal · pago MP dinero en cuenta · screenshot</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Septiembre</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="19" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Metrogas — INVALMAR (10139236800)</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>5582</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Mercado Pago</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Metrogas INVALMAR · pago MP screenshot · mes=cobro</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Septiembre</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/OHIGGINS/Gastos_OHIGGINS_2026.xlsx
+++ b/OHIGGINS/Gastos_OHIGGINS_2026.xlsx
@@ -160,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -181,6 +181,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -772,8 +773,12 @@
       <c r="J7" s="5" t="n">
         <v>88891</v>
       </c>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
+      <c r="K7" s="5" t="n">
+        <v>88891</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>88891</v>
+      </c>
       <c r="M7" s="5" t="n"/>
       <c r="N7" s="5" t="n"/>
       <c r="O7" s="5" t="n"/>
@@ -1172,7 +1177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2020,6 +2025,72 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="18" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>IMPUESTOS</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ABL</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ABL — partida 3016365 · CUOTA 08/2026</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>88891</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mercado Pago</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>3016365 · ceil desde $88.890,01 · 1° vto 14/08/2026 · 2° vto 31/08 $100.779</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>IMPUESTOS</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ABL</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ABL — partida 3016365 · CUOTA 09/2026</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>88891</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mercado Pago</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>3016365 · ceil desde $88.890,01 · 1° vto 14/09/2026 · 2° vto 30/09 $100.779 · PDF AGIP _inbox</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/OHIGGINS/Gastos_OHIGGINS_2026.xlsx
+++ b/OHIGGINS/Gastos_OHIGGINS_2026.xlsx
@@ -779,9 +779,15 @@
       <c r="L7" s="5" t="n">
         <v>88891</v>
       </c>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
+      <c r="M7" s="5" t="n">
+        <v>88891</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>88891</v>
+      </c>
+      <c r="O7" s="5" t="n">
+        <v>88891</v>
+      </c>
       <c r="P7" s="5">
         <f>SUM(D6:O6)</f>
         <v/>
@@ -1177,7 +1183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2091,6 +2097,105 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="18" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>IMPUESTOS</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ABL</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ABL — partida 3016365 · CUOTA 10/2026</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>88891</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>3016365 · ceil desde $88.890,01 · 1° vto 14/10/2026 · AGIP ConsultaABL 2026-10-06 · PENDIENTE · sin deuda vencida previa</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="n">
+        <v>46339</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>IMPUESTOS</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ABL</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ABL — partida 3016365 · CUOTA 11/2026</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>88891</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>3016365 · ceil desde $88.890,01 · 1° vto 13/11/2026 · AGIP ConsultaABL 2026-10-06 · PENDIENTE · sin deuda vencida previa</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="n">
+        <v>46370</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>IMPUESTOS</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ABL</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ABL — partida 3016365 · CUOTA 12/2026</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>88891</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>3016365 · ceil desde $88.890,01 · 1° vto 14/12/2026 · AGIP ConsultaABL 2026-10-06 · PENDIENTE · sin deuda vencida previa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/OHIGGINS/Gastos_OHIGGINS_2026.xlsx
+++ b/OHIGGINS/Gastos_OHIGGINS_2026.xlsx
@@ -582,6 +582,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -865,9 +866,15 @@
       <c r="J9" s="5" t="n">
         <v>5208</v>
       </c>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
+      <c r="K9" s="5" t="n">
+        <v>5209</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>5582</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>5589</v>
+      </c>
       <c r="N9" s="5" t="n"/>
       <c r="O9" s="5" t="n"/>
       <c r="P9" s="5">
@@ -1181,7 +1188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1200,6 +1207,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="15" t="inlineStr">
         <is>
@@ -2125,6 +2133,105 @@
       <c r="G30" t="inlineStr">
         <is>
           <t>cuenta 9267222037</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>SERVICIOS</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="inlineStr">
+        <is>
+          <t>Metrogas — INVALMAR SRL · O'Higgins 2225 · venc. 10/08/2026</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>5209</v>
+      </c>
+      <c r="F31" s="17" t="inlineStr">
+        <is>
+          <t>Factura Gmail Metrogas · sin pago MP aún</t>
+        </is>
+      </c>
+      <c r="G31" s="17" t="inlineStr">
+        <is>
+          <t>10139236800 · medidor 8683287 · emisión 30/07 · período 02/06–01/07 · Débito NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>SERVICIOS</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="D32" s="17" t="inlineStr">
+        <is>
+          <t>Metrogas — INVALMAR SRL · O'Higgins 2225 · venc. 14/09/2026</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>5582</v>
+      </c>
+      <c r="F32" s="17" t="inlineStr">
+        <is>
+          <t>Factura Gmail Metrogas · sin pago MP aún</t>
+        </is>
+      </c>
+      <c r="G32" s="17" t="inlineStr">
+        <is>
+          <t>10139236800 · medidor 8683287 · emisión 02/09 · período 02/07–30/07 · Débito NO · PENDIENTE pago</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>SERVICIOS</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="D33" s="17" t="inlineStr">
+        <is>
+          <t>Metrogas — INVALMAR SRL · O'Higgins 2225 · venc. 13/10/2026</t>
+        </is>
+      </c>
+      <c r="E33" s="17" t="n">
+        <v>5589</v>
+      </c>
+      <c r="F33" s="17" t="inlineStr">
+        <is>
+          <t>Factura Gmail Metrogas · sin pago MP aún</t>
+        </is>
+      </c>
+      <c r="G33" s="17" t="inlineStr">
+        <is>
+          <t>10139236800 · medidor 8683287 · emisión 30/09 · período 31/07–31/08 · Débito NO · PENDIENTE pago</t>
         </is>
       </c>
     </row>

--- a/OHIGGINS/Gastos_OHIGGINS_2026.xlsx
+++ b/OHIGGINS/Gastos_OHIGGINS_2026.xlsx
@@ -582,7 +582,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -704,6 +703,9 @@
       </c>
       <c r="K5" t="n">
         <v>722979</v>
+      </c>
+      <c r="L5" t="n">
+        <v>722978</v>
       </c>
     </row>
     <row r="6">
@@ -740,8 +742,12 @@
         <v>56200</v>
       </c>
       <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
+      <c r="L6" s="5" t="n">
+        <v>57246</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>76044</v>
+      </c>
       <c r="N6" s="5" t="n"/>
       <c r="O6" s="5" t="n"/>
       <c r="P6" s="5">
@@ -823,11 +829,15 @@
         <v>16904</v>
       </c>
       <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
+      <c r="K8" s="5" t="n">
+        <v>19492</v>
+      </c>
       <c r="L8" s="5" t="n">
         <v>18236</v>
       </c>
-      <c r="M8" s="5" t="n"/>
+      <c r="M8" s="5" t="n">
+        <v>12004</v>
+      </c>
       <c r="N8" s="5" t="n"/>
       <c r="O8" s="5" t="n"/>
       <c r="P8" s="5">
@@ -1188,7 +1198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2235,6 +2245,171 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="18" t="n">
+        <v>46243</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SERVICIOS</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>LUZ</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Edenor — Marta Chagas · cobro BBVA 09/08/2026</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>19492</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Débito BBVA Visa 3200</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>cuenta 9267222037 · ARS 19.491,89</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="18" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SERVICIOS</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>LUZ</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Edenor — Marta Chagas · venc. 09/10/2026 · factura Gmail 30/09</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>12004</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Débito BBVA (pendiente confirmación cobro)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>cuenta 9267222037 · $12.003,68</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="18" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SERVICIOS</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>TV CABLE-INTERNET</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Personal — Pago directo · venc. 01/09/2026</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>57246</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Personal factura digital Gmail</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Fibra Flow + Telefonía · $57.245,01</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SERVICIOS</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>TV CABLE-INTERNET</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Personal — Pago directo · venc. 01/10/2026</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>76044</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Personal factura digital Gmail</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Fibra Flow + Telefonía · $76.043,51</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SERVICIOS</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EXPENSAS</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Expensas OHIGGINS 2219 piso 8 · septiembre (liq. Kalmus · venc ~10-oct)</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>722978</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Pendiente pago / Kalmus Gmail</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>UF08 SANES · período septiembre 2026 · PDF sep26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/OHIGGINS/Gastos_OHIGGINS_2026.xlsx
+++ b/OHIGGINS/Gastos_OHIGGINS_2026.xlsx
@@ -160,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -182,6 +182,7 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -813,22 +814,22 @@
         </is>
       </c>
       <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n">
         <v>116475</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="G8" s="5" t="n">
         <v>21474</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="H8" s="5" t="n">
         <v>14546</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="I8" s="5" t="n">
         <v>10578</v>
       </c>
-      <c r="I8" s="5" t="n">
+      <c r="J8" s="5" t="n">
         <v>16904</v>
       </c>
-      <c r="J8" s="5" t="n"/>
       <c r="K8" s="5" t="n">
         <v>19492</v>
       </c>
@@ -1217,47 +1218,79 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Monto</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Forma de pago</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Partida / N° Cliente / Notas</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
+      <c r="A3" s="19" t="n">
+        <v>46066</v>
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>Tipo</t>
+          <t>IMPUESTOS</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>Categoría</t>
+          <t>ABL</t>
         </is>
       </c>
       <c r="D3" s="15" t="inlineStr">
         <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>Monto</t>
-        </is>
+          <t>ABL — partida 3016365</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="n">
+        <v>83757</v>
       </c>
       <c r="F3" s="15" t="inlineStr">
         <is>
-          <t>Forma de pago</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
       <c r="G3" s="15" t="inlineStr">
         <is>
-          <t>Partida / N° Cliente / Notas</t>
+          <t>3016365</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="n">
-        <v>46066</v>
+        <v>46084</v>
       </c>
       <c r="B4" s="17" t="inlineStr">
         <is>
@@ -1275,7 +1308,7 @@
         </is>
       </c>
       <c r="E4" s="17" t="n">
-        <v>83757</v>
+        <v>88141</v>
       </c>
       <c r="F4" s="17" t="inlineStr">
         <is>
@@ -1290,7 +1323,7 @@
     </row>
     <row r="5">
       <c r="A5" s="16" t="n">
-        <v>46084</v>
+        <v>46203</v>
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
@@ -1308,7 +1341,7 @@
         </is>
       </c>
       <c r="E5" s="17" t="n">
-        <v>88141</v>
+        <v>100779</v>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
@@ -1323,7 +1356,7 @@
     </row>
     <row r="6">
       <c r="A6" s="16" t="n">
-        <v>46203</v>
+        <v>46217</v>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
@@ -1341,7 +1374,7 @@
         </is>
       </c>
       <c r="E6" s="17" t="n">
-        <v>100779</v>
+        <v>88891</v>
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
@@ -1356,40 +1389,40 @@
     </row>
     <row r="7">
       <c r="A7" s="16" t="n">
-        <v>46217</v>
+        <v>46118</v>
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>IMPUESTOS</t>
+          <t>SERVICIOS</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>ABL</t>
+          <t>GAS</t>
         </is>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t>ABL — partida 3016365</t>
+          <t>Metrogas — INVALMAR SRL · O'Higgins 2225</t>
         </is>
       </c>
       <c r="E7" s="17" t="n">
-        <v>88891</v>
+        <v>4850</v>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>Mercado Pago</t>
+          <t>Mercado Pago / Gmail</t>
         </is>
       </c>
       <c r="G7" s="17" t="inlineStr">
         <is>
-          <t>3016365</t>
+          <t>10139236800</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="16" t="n">
-        <v>46081</v>
+        <v>46146</v>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
@@ -1398,31 +1431,31 @@
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>LUZ</t>
+          <t>GAS</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>Edenor — Marta Chagas · O'Higgins 2225</t>
+          <t>Metrogas — INVALMAR SRL · O'Higgins 2225</t>
         </is>
       </c>
       <c r="E8" s="17" t="n">
-        <v>116475</v>
+        <v>4935</v>
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t>Factura digital Gmail / BBVA</t>
+          <t>Mercado Pago / Gmail</t>
         </is>
       </c>
       <c r="G8" s="17" t="inlineStr">
         <is>
-          <t>9267222037</t>
+          <t>10139236800</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="16" t="n">
-        <v>46110</v>
+        <v>46175</v>
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
@@ -1431,31 +1464,31 @@
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>LUZ</t>
+          <t>GAS</t>
         </is>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>Edenor — Marta Chagas · O'Higgins 2225</t>
+          <t>Metrogas — INVALMAR SRL · O'Higgins 2225</t>
         </is>
       </c>
       <c r="E9" s="17" t="n">
-        <v>21474</v>
+        <v>4984</v>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>Factura digital Gmail / BBVA</t>
+          <t>Mercado Pago / Gmail</t>
         </is>
       </c>
       <c r="G9" s="17" t="inlineStr">
         <is>
-          <t>9267222037</t>
+          <t>10139236800</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="16" t="n">
-        <v>46142</v>
+        <v>46209</v>
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
@@ -1464,31 +1497,31 @@
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>LUZ</t>
+          <t>GAS</t>
         </is>
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t>Edenor — Marta Chagas · O'Higgins 2225</t>
+          <t>Metrogas — INVALMAR SRL · O'Higgins 2225</t>
         </is>
       </c>
       <c r="E10" s="17" t="n">
-        <v>14546</v>
+        <v>5208</v>
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t>Factura digital Gmail / BBVA</t>
+          <t>Mercado Pago / Gmail</t>
         </is>
       </c>
       <c r="G10" s="17" t="inlineStr">
         <is>
-          <t>9267222037</t>
+          <t>10139236800</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="16" t="n">
-        <v>46171</v>
+        <v>46032</v>
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
@@ -1497,31 +1530,31 @@
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>LUZ</t>
+          <t>TV CABLE-INTERNET</t>
         </is>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t>Edenor — Marta Chagas · O'Higgins 2225</t>
+          <t>Personal — Pago directo</t>
         </is>
       </c>
       <c r="E11" s="17" t="n">
-        <v>10578</v>
+        <v>34921</v>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>Factura digital Gmail / BBVA</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
       <c r="G11" s="17" t="inlineStr">
         <is>
-          <t>9267222037</t>
+          <t>Personal flow · resumen MP</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="16" t="n">
-        <v>46200</v>
+        <v>46122</v>
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
@@ -1530,31 +1563,31 @@
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>LUZ</t>
+          <t>TV CABLE-INTERNET</t>
         </is>
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t>Edenor — Marta Chagas · O'Higgins 2225</t>
+          <t>Personal — Pago directo</t>
         </is>
       </c>
       <c r="E12" s="17" t="n">
-        <v>16904</v>
+        <v>101114</v>
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>Factura digital Gmail / BBVA</t>
+          <t>Mercado Pago · incluye saldo Mar débito rechazado 09/04 + factura Abr</t>
         </is>
       </c>
       <c r="G12" s="17" t="inlineStr">
         <is>
-          <t>9267222037</t>
+          <t>resumen MP · factura $101.113,85</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="16" t="n">
-        <v>46118</v>
+        <v>46154</v>
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
@@ -1563,31 +1596,31 @@
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>GAS</t>
+          <t>TV CABLE-INTERNET</t>
         </is>
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t>Metrogas — INVALMAR SRL · O'Higgins 2225</t>
+          <t>Personal — Pago directo</t>
         </is>
       </c>
       <c r="E13" s="17" t="n">
-        <v>4850</v>
+        <v>53245</v>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>Mercado Pago / Gmail</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
       <c r="G13" s="17" t="inlineStr">
         <is>
-          <t>10139236800</t>
+          <t>resumen MP</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="16" t="n">
-        <v>46146</v>
+        <v>46184</v>
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
@@ -1596,31 +1629,31 @@
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>GAS</t>
+          <t>TV CABLE-INTERNET</t>
         </is>
       </c>
       <c r="D14" s="17" t="inlineStr">
         <is>
-          <t>Metrogas — INVALMAR SRL · O'Higgins 2225</t>
+          <t>Personal — Pago directo</t>
         </is>
       </c>
       <c r="E14" s="17" t="n">
-        <v>4935</v>
+        <v>55106</v>
       </c>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t>Mercado Pago / Gmail</t>
+          <t>Mercado Pago</t>
         </is>
       </c>
       <c r="G14" s="17" t="inlineStr">
         <is>
-          <t>10139236800</t>
+          <t>resumen MP</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="16" t="n">
-        <v>46175</v>
+        <v>46217</v>
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
@@ -1629,31 +1662,31 @@
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>GAS</t>
+          <t>TV CABLE-INTERNET</t>
         </is>
       </c>
       <c r="D15" s="17" t="inlineStr">
         <is>
-          <t>Metrogas — INVALMAR SRL · O'Higgins 2225</t>
+          <t>Personal — Pago directo</t>
         </is>
       </c>
       <c r="E15" s="17" t="n">
-        <v>4984</v>
+        <v>56200</v>
       </c>
       <c r="F15" s="17" t="inlineStr">
         <is>
-          <t>Mercado Pago / Gmail</t>
+          <t>Mercado Pago · paga factura venc. 03/08/2026 (cubre Agosto)</t>
         </is>
       </c>
       <c r="G15" s="17" t="inlineStr">
         <is>
-          <t>10139236800</t>
+          <t>Personal factura Gmail 14/07 · $56.200,00 venc 03/08</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="16" t="n">
-        <v>46209</v>
+        <v>46031</v>
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
@@ -1662,31 +1695,31 @@
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>GAS</t>
+          <t>EXPENSAS</t>
         </is>
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
-          <t>Metrogas — INVALMAR SRL · O'Higgins 2225</t>
+          <t>Expensas OHIGGINS 2219 piso 8 · enero</t>
         </is>
       </c>
       <c r="E16" s="17" t="n">
-        <v>5208</v>
+        <v>376564</v>
       </c>
       <c r="F16" s="17" t="inlineStr">
         <is>
-          <t>Mercado Pago / Gmail</t>
+          <t>Mercado Pago — Consorcio De Copropi</t>
         </is>
       </c>
       <c r="G16" s="17" t="inlineStr">
         <is>
-          <t>10139236800</t>
+          <t>Kalmus</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="16" t="n">
-        <v>46032</v>
+        <v>46059</v>
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
@@ -1695,31 +1728,31 @@
       </c>
       <c r="C17" s="17" t="inlineStr">
         <is>
-          <t>TV CABLE-INTERNET</t>
+          <t>EXPENSAS</t>
         </is>
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
-          <t>Personal — Pago directo</t>
+          <t>Expensas OHIGGINS 2219 piso 8 · febrero</t>
         </is>
       </c>
       <c r="E17" s="17" t="n">
-        <v>34921</v>
+        <v>395551</v>
       </c>
       <c r="F17" s="17" t="inlineStr">
         <is>
-          <t>Mercado Pago</t>
+          <t>Mercado Pago — Consorcio De Copropi</t>
         </is>
       </c>
       <c r="G17" s="17" t="inlineStr">
         <is>
-          <t>Personal flow · resumen MP</t>
+          <t>Kalmus</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="16" t="n">
-        <v>46122</v>
+        <v>46091</v>
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
@@ -1728,31 +1761,31 @@
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>TV CABLE-INTERNET</t>
+          <t>EXPENSAS</t>
         </is>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
-          <t>Personal — Pago directo</t>
+          <t>Expensas OHIGGINS 2219 piso 8 · marzo</t>
         </is>
       </c>
       <c r="E18" s="17" t="n">
-        <v>101114</v>
+        <v>402934</v>
       </c>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t>Mercado Pago</t>
+          <t>Mercado Pago — Consorcio De Copropi</t>
         </is>
       </c>
       <c r="G18" s="17" t="inlineStr">
         <is>
-          <t>resumen MP</t>
+          <t>Kalmus</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="16" t="n">
-        <v>46154</v>
+        <v>46120</v>
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
@@ -1761,31 +1794,31 @@
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>TV CABLE-INTERNET</t>
+          <t>EXPENSAS</t>
         </is>
       </c>
       <c r="D19" s="17" t="inlineStr">
         <is>
-          <t>Personal — Pago directo</t>
+          <t>Expensas OHIGGINS 2219 piso 8 · abril</t>
         </is>
       </c>
       <c r="E19" s="17" t="n">
-        <v>53245</v>
+        <v>570841</v>
       </c>
       <c r="F19" s="17" t="inlineStr">
         <is>
-          <t>Mercado Pago</t>
+          <t>Banco — Transferencia</t>
         </is>
       </c>
       <c r="G19" s="17" t="inlineStr">
         <is>
-          <t>resumen MP</t>
+          <t>Gmail Sent 8-abr</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="16" t="n">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
@@ -1794,31 +1827,31 @@
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>TV CABLE-INTERNET</t>
+          <t>EXPENSAS</t>
         </is>
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
-          <t>Personal — Pago directo</t>
+          <t>Expensas OHIGGINS 2219 piso 8 · mayo (pago 10-jun)</t>
         </is>
       </c>
       <c r="E20" s="17" t="n">
-        <v>55106</v>
+        <v>666347</v>
       </c>
       <c r="F20" s="17" t="inlineStr">
         <is>
-          <t>Mercado Pago</t>
+          <t>Mercado Pago — Consorcio De Copropi</t>
         </is>
       </c>
       <c r="G20" s="17" t="inlineStr">
         <is>
-          <t>resumen MP</t>
+          <t>Gmail Sent</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="16" t="n">
-        <v>46217</v>
+        <v>46212</v>
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
@@ -1827,31 +1860,31 @@
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>TV CABLE-INTERNET</t>
+          <t>EXPENSAS</t>
         </is>
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>
-          <t>Personal — Pago directo</t>
+          <t>Expensas OHIGGINS 2219 piso 8 · junio (pago 9-jul)</t>
         </is>
       </c>
       <c r="E21" s="17" t="n">
-        <v>56200</v>
+        <v>829490</v>
       </c>
       <c r="F21" s="17" t="inlineStr">
         <is>
-          <t>Mercado Pago</t>
+          <t>Mercado Pago — Consorcio De Copropi</t>
         </is>
       </c>
       <c r="G21" s="17" t="inlineStr">
         <is>
-          <t>resumen MP</t>
+          <t>Gmail Sent</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="16" t="n">
-        <v>46031</v>
+        <v>46244</v>
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
@@ -1865,11 +1898,11 @@
       </c>
       <c r="D22" s="17" t="inlineStr">
         <is>
-          <t>Expensas OHIGGINS 2219 piso 8 · enero</t>
+          <t>Expensas OHIGGINS 2219 piso 8 · julio (pago 10-ago)</t>
         </is>
       </c>
       <c r="E22" s="17" t="n">
-        <v>376564</v>
+        <v>907569</v>
       </c>
       <c r="F22" s="17" t="inlineStr">
         <is>
@@ -1878,13 +1911,13 @@
       </c>
       <c r="G22" s="17" t="inlineStr">
         <is>
-          <t>Kalmus</t>
+          <t>Kalmus · Gmail Sent · recibo $907.568,08</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="16" t="n">
-        <v>46059</v>
+        <v>46276</v>
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
@@ -1898,11 +1931,11 @@
       </c>
       <c r="D23" s="17" t="inlineStr">
         <is>
-          <t>Expensas OHIGGINS 2219 piso 8 · febrero</t>
+          <t>Expensas OHIGGINS 2219 piso 8 · agosto (pago 11-sep)</t>
         </is>
       </c>
       <c r="E23" s="17" t="n">
-        <v>395551</v>
+        <v>722979</v>
       </c>
       <c r="F23" s="17" t="inlineStr">
         <is>
@@ -1911,13 +1944,13 @@
       </c>
       <c r="G23" s="17" t="inlineStr">
         <is>
-          <t>Kalmus</t>
+          <t>Kalmus · Gmail Sent · MP $722.978,08 · Galicia</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="16" t="n">
-        <v>46091</v>
+        <v>46244</v>
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
@@ -1926,31 +1959,31 @@
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>EXPENSAS</t>
+          <t>GAS</t>
         </is>
       </c>
       <c r="D24" s="17" t="inlineStr">
         <is>
-          <t>Expensas OHIGGINS 2219 piso 8 · marzo</t>
+          <t>Metrogas — INVALMAR SRL · O'Higgins 2225 · venc. 10/08/2026</t>
         </is>
       </c>
       <c r="E24" s="17" t="n">
-        <v>402934</v>
+        <v>5209</v>
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>
-          <t>Mercado Pago — Consorcio De Copropi</t>
+          <t>Factura Gmail Metrogas · sin pago MP aún</t>
         </is>
       </c>
       <c r="G24" s="17" t="inlineStr">
         <is>
-          <t>Kalmus</t>
+          <t>10139236800 · medidor 8683287 · emisión 30/07 · período 02/06–01/07 · Débito NO</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="16" t="n">
-        <v>46120</v>
+        <v>46279</v>
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
@@ -1959,31 +1992,31 @@
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>EXPENSAS</t>
+          <t>GAS</t>
         </is>
       </c>
       <c r="D25" s="17" t="inlineStr">
         <is>
-          <t>Expensas OHIGGINS 2219 piso 8 · abril</t>
+          <t>Metrogas — INVALMAR SRL · O'Higgins 2225 · venc. 14/09/2026</t>
         </is>
       </c>
       <c r="E25" s="17" t="n">
-        <v>570841</v>
+        <v>5582</v>
       </c>
       <c r="F25" s="17" t="inlineStr">
         <is>
-          <t>Banco — Transferencia</t>
+          <t>Factura Gmail Metrogas · sin pago MP aún</t>
         </is>
       </c>
       <c r="G25" s="17" t="inlineStr">
         <is>
-          <t>Gmail Sent 8-abr</t>
+          <t>10139236800 · medidor 8683287 · emisión 02/09 · período 02/07–30/07 · Débito NO · PENDIENTE pago</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="16" t="n">
-        <v>46183</v>
+        <v>46308</v>
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
@@ -1992,31 +2025,31 @@
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>EXPENSAS</t>
+          <t>GAS</t>
         </is>
       </c>
       <c r="D26" s="17" t="inlineStr">
         <is>
-          <t>Expensas OHIGGINS 2219 piso 8 · mayo (pago 10-jun)</t>
+          <t>Metrogas — INVALMAR SRL · O'Higgins 2225 · venc. 13/10/2026</t>
         </is>
       </c>
       <c r="E26" s="17" t="n">
-        <v>666347</v>
+        <v>5589</v>
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>Mercado Pago — Consorcio De Copropi</t>
+          <t>Factura Gmail Metrogas · sin pago MP aún</t>
         </is>
       </c>
       <c r="G26" s="17" t="inlineStr">
         <is>
-          <t>Gmail Sent</t>
+          <t>10139236800 · medidor 8683287 · emisión 30/09 · período 31/07–31/08 · Débito NO · PENDIENTE pago</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="16" t="n">
-        <v>46212</v>
+        <v>46266</v>
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
@@ -2025,31 +2058,31 @@
       </c>
       <c r="C27" s="17" t="inlineStr">
         <is>
-          <t>EXPENSAS</t>
+          <t>TV CABLE-INTERNET</t>
         </is>
       </c>
       <c r="D27" s="17" t="inlineStr">
         <is>
-          <t>Expensas OHIGGINS 2219 piso 8 · junio (pago 9-jul)</t>
+          <t>Personal — Pago directo · venc. 01/09/2026</t>
         </is>
       </c>
       <c r="E27" s="17" t="n">
-        <v>829490</v>
+        <v>57246</v>
       </c>
       <c r="F27" s="17" t="inlineStr">
         <is>
-          <t>Mercado Pago — Consorcio De Copropi</t>
+          <t>Personal factura digital Gmail</t>
         </is>
       </c>
       <c r="G27" s="17" t="inlineStr">
         <is>
-          <t>Gmail Sent</t>
+          <t>Fibra Flow + Telefonía · $57.245,01</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="18" t="n">
-        <v>46244</v>
+        <v>46296</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2058,31 +2091,31 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>EXPENSAS</t>
+          <t>TV CABLE-INTERNET</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Expensas OHIGGINS 2219 piso 8 · julio (pago 10-ago)</t>
+          <t>Personal — Pago directo · venc. 01/10/2026</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>907569</v>
+        <v>76044</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mercado Pago — Consorcio De Copropi</t>
+          <t>Personal factura digital Gmail</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Kalmus · Gmail Sent · recibo $907.568,08</t>
+          <t>Fibra Flow + Telefonía · $76.043,51</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="18" t="n">
-        <v>46276</v>
+        <v>46305</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2096,26 +2129,26 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Expensas OHIGGINS 2219 piso 8 · agosto (pago 11-sep)</t>
+          <t>Expensas OHIGGINS 2219 piso 8 · septiembre (liq. Kalmus · venc ~10-oct)</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>722979</v>
+        <v>722978</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mercado Pago — Consorcio De Copropi</t>
+          <t>Pendiente pago / Kalmus Gmail</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Kalmus · Gmail Sent · MP $722.978,08 · Galicia</t>
+          <t>UF08 SANES · período septiembre 2026 · PDF sep26</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="18" t="n">
-        <v>46274</v>
+        <v>46093</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2129,26 +2162,26 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Edenor — Marta Chagas · cobro BBVA 09/09/2026</t>
+          <t>Edenor — Marta Chagas · cobro BBVA 12/03/2026</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>18236</v>
+        <v>116475</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Débito BBVA Visa 3200</t>
+          <t>Débito BBVA Visa · resumen</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>cuenta 9267222037</t>
+          <t>cuenta 9267222037 · ARS 116.474,99</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="16" t="n">
-        <v>46244</v>
+        <v>46122</v>
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
@@ -2157,31 +2190,31 @@
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>GAS</t>
+          <t>LUZ</t>
         </is>
       </c>
       <c r="D31" s="17" t="inlineStr">
         <is>
-          <t>Metrogas — INVALMAR SRL · O'Higgins 2225 · venc. 10/08/2026</t>
+          <t>Edenor — Marta Chagas · cobro BBVA 10/04/2026</t>
         </is>
       </c>
       <c r="E31" s="17" t="n">
-        <v>5209</v>
+        <v>21474</v>
       </c>
       <c r="F31" s="17" t="inlineStr">
         <is>
-          <t>Factura Gmail Metrogas · sin pago MP aún</t>
+          <t>Débito BBVA Visa · resumen</t>
         </is>
       </c>
       <c r="G31" s="17" t="inlineStr">
         <is>
-          <t>10139236800 · medidor 8683287 · emisión 30/07 · período 02/06–01/07 · Débito NO</t>
+          <t>cuenta 9267222037 · ARS 21.473,25</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="16" t="n">
-        <v>46279</v>
+        <v>46154</v>
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
@@ -2190,31 +2223,31 @@
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>GAS</t>
+          <t>LUZ</t>
         </is>
       </c>
       <c r="D32" s="17" t="inlineStr">
         <is>
-          <t>Metrogas — INVALMAR SRL · O'Higgins 2225 · venc. 14/09/2026</t>
+          <t>Edenor — Marta Chagas · cobro BBVA 12/05/2026</t>
         </is>
       </c>
       <c r="E32" s="17" t="n">
-        <v>5582</v>
+        <v>14546</v>
       </c>
       <c r="F32" s="17" t="inlineStr">
         <is>
-          <t>Factura Gmail Metrogas · sin pago MP aún</t>
+          <t>Débito BBVA Visa · resumen</t>
         </is>
       </c>
       <c r="G32" s="17" t="inlineStr">
         <is>
-          <t>10139236800 · medidor 8683287 · emisión 02/09 · período 02/07–30/07 · Débito NO · PENDIENTE pago</t>
+          <t>cuenta 9267222037 · ARS 14.545,83</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="16" t="n">
-        <v>46308</v>
+        <v>46183</v>
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
@@ -2223,31 +2256,31 @@
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>GAS</t>
+          <t>LUZ</t>
         </is>
       </c>
       <c r="D33" s="17" t="inlineStr">
         <is>
-          <t>Metrogas — INVALMAR SRL · O'Higgins 2225 · venc. 13/10/2026</t>
+          <t>Edenor — Marta Chagas · cobro BBVA 10/06/2026</t>
         </is>
       </c>
       <c r="E33" s="17" t="n">
-        <v>5589</v>
+        <v>10578</v>
       </c>
       <c r="F33" s="17" t="inlineStr">
         <is>
-          <t>Factura Gmail Metrogas · sin pago MP aún</t>
+          <t>Débito BBVA Visa · resumen</t>
         </is>
       </c>
       <c r="G33" s="17" t="inlineStr">
         <is>
-          <t>10139236800 · medidor 8683287 · emisión 30/09 · período 31/07–31/08 · Débito NO · PENDIENTE pago</t>
+          <t>cuenta 9267222037 · ARS 10.577,07</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="18" t="n">
-        <v>46243</v>
+        <v>46216</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -2261,26 +2294,26 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Edenor — Marta Chagas · cobro BBVA 09/08/2026</t>
+          <t>Edenor — Marta Chagas · venc. 13/07/2026 · factura Gmail</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>19492</v>
+        <v>16904</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Débito BBVA Visa 3200</t>
+          <t>Factura digital Gmail (débito auto vencimiento)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>cuenta 9267222037 · ARS 19.491,89</t>
+          <t>cuenta 9267222037 · ARS 16.903,23</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="18" t="n">
-        <v>46304</v>
+        <v>46243</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -2294,26 +2327,26 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Edenor — Marta Chagas · venc. 09/10/2026 · factura Gmail 30/09</t>
+          <t>Edenor — Marta Chagas · cobro BBVA 09/08/2026</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>12004</v>
+        <v>19492</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Débito BBVA (pendiente confirmación cobro)</t>
+          <t>Débito BBVA Visa 3200</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>cuenta 9267222037 · $12.003,68</t>
+          <t>cuenta 9267222037 · ARS 19.491,89</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="18" t="n">
-        <v>46266</v>
+        <v>46274</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -2322,31 +2355,31 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>TV CABLE-INTERNET</t>
+          <t>LUZ</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Personal — Pago directo · venc. 01/09/2026</t>
+          <t>Edenor — Marta Chagas · cobro BBVA 09/09/2026</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>57246</v>
+        <v>18236</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Personal factura digital Gmail</t>
+          <t>Débito BBVA Visa 3200</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fibra Flow + Telefonía · $57.245,01</t>
+          <t>cuenta 9267222037 · ARS 18.235,37</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="18" t="n">
-        <v>46296</v>
+        <v>46304</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -2355,60 +2388,30 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TV CABLE-INTERNET</t>
+          <t>LUZ</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Personal — Pago directo · venc. 01/10/2026</t>
+          <t>Edenor — Marta Chagas · venc. 09/10/2026 · factura Gmail 30/09</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>76044</v>
+        <v>12004</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Personal factura digital Gmail</t>
+          <t>Débito BBVA (pendiente confirmación cobro)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fibra Flow + Telefonía · $76.043,51</t>
+          <t>cuenta 9267222037 · $12.003,68</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="n">
-        <v>46305</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>SERVICIOS</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>EXPENSAS</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Expensas OHIGGINS 2219 piso 8 · septiembre (liq. Kalmus · venc ~10-oct)</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>722978</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Pendiente pago / Kalmus Gmail</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>UF08 SANES · período septiembre 2026 · PDF sep26</t>
-        </is>
-      </c>
+      <c r="A38" s="18" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/OHIGGINS/Gastos_OHIGGINS_2026.xlsx
+++ b/OHIGGINS/Gastos_OHIGGINS_2026.xlsx
@@ -160,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -181,6 +181,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -697,6 +698,9 @@
       <c r="I5" t="n">
         <v>829490</v>
       </c>
+      <c r="L5" t="n">
+        <v>722978</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1172,7 +1176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2020,6 +2024,39 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="18" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SERVICIOS</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EXPENSAS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Expensas OHIGGINS 2219 piso 8 · septiembre (pago 10-oct)</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>722978</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mercado Pago — Consorcio De Copropietarios O Higgins 22</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ceil desde $722.977,08 · Galicia CBU 0070692220000003412822 · CUIT 30-60701536-4 · op MP 183430574930</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/OHIGGINS/Gastos_OHIGGINS_2026.xlsx
+++ b/OHIGGINS/Gastos_OHIGGINS_2026.xlsx
@@ -2048,12 +2048,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mercado Pago — Consorcio De Copropietarios O Higgins 22</t>
+          <t>Mercado Pago — Dinero en cuenta — Consorcio De Copropietarios O Higgins 22</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>ceil desde $722.977,08 · Galicia CBU 0070692220000003412822 · CUIT 30-60701536-4 · op MP 183430574930</t>
+          <t>ceil desde $722.977,08 · Galicia CBU 0070692220000003412822 · CUIT 30-60701536-4 · op MP 183430574930 · MP dinero en cuenta · período septiembre 2026</t>
         </is>
       </c>
     </row>

--- a/OHIGGINS/Gastos_OHIGGINS_2026.xlsx
+++ b/OHIGGINS/Gastos_OHIGGINS_2026.xlsx
@@ -17,10 +17,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -160,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -181,6 +182,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -815,9 +817,15 @@
         <v>16904</v>
       </c>
       <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
+      <c r="K8" s="5" t="n">
+        <v>19492</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>18236</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>12004</v>
+      </c>
       <c r="N8" s="5" t="n"/>
       <c r="O8" s="5" t="n"/>
       <c r="P8" s="5">
@@ -1172,7 +1180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2020,6 +2028,105 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="18" t="n">
+        <v>46243</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SERVICIOS</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>LUZ</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Edenor — Marta Chagas · O'Higgins · débito BBVA 09/08/2026</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>19492</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Débito BBVA Visa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>9267222037 · Gmail Compra aprobada</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SERVICIOS</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>LUZ</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Edenor — Marta Chagas · O'Higgins · débito BBVA 09/09/2026</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>18236</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Débito BBVA Visa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>9267222037 · Gmail Compra aprobada</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SERVICIOS</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>LUZ</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Edenor — Marta Chagas · O'Higgins · débito BBVA 09/10/2026</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>12004</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Débito BBVA Visa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>9267222037 · Gmail Compra aprobada</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
